--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487404_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487404_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8045</v>
+        <v>2.7675</v>
       </c>
       <c r="E2" t="n">
-        <v>1.457</v>
+        <v>1.4735</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3475</v>
+        <v>1.294</v>
       </c>
       <c r="G2" t="n">
         <v>3.0731</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3262</v>
+        <v>-0.3632</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0129</v>
+        <v>0.0035</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3132</v>
+        <v>-0.3667</v>
       </c>
       <c r="V2" t="n">
         <v>0.0576</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.596</v>
+        <v>1.4968</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1931</v>
+        <v>-0.4518</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7891</v>
+        <v>1.9486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4385</v>
+        <v>0.8066</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3041</v>
+        <v>-1.5924</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7427</v>
+        <v>2.399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1521</v>
+        <v>0.9233</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1021</v>
+        <v>-1.3236</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0501</v>
+        <v>2.2469</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2864</v>
+        <v>-0.1167</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4062</v>
+        <v>-0.2687</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6926</v>
+        <v>0.152</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1575</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8299</v>
+        <v>-0.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3276</v>
+        <v>-0.3045</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9988</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5025</v>
+        <v>1.3387</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3659</v>
+        <v>0.6401</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8684</v>
+        <v>0.6986</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8066</v>
+        <v>1.6697</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5924</v>
+        <v>0.6489</v>
       </c>
       <c r="I4" t="n">
-        <v>2.399</v>
+        <v>1.0208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9233</v>
+        <v>2.0593</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3236</v>
+        <v>1.327</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2469</v>
+        <v>0.7323</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1167</v>
+        <v>-0.3896</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2687</v>
+        <v>-0.6781</v>
       </c>
       <c r="O4" t="n">
-        <v>0.152</v>
+        <v>0.2885</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4988</v>
+        <v>-0.6052</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1141</v>
+        <v>-0.2441</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3847</v>
+        <v>-0.3611</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9988</v>
+        <v>0.6659</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9988</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3501</v>
+        <v>1.2726</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4316</v>
+        <v>-3.1081</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7817</v>
+        <v>4.3807</v>
       </c>
       <c r="G5" t="n">
         <v>0.2096</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0762</v>
+        <v>-0.1536</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.31</v>
+        <v>0.0135</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2338</v>
+        <v>-0.1672</v>
       </c>
       <c r="V5" t="n">
         <v>1.2166</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9293</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2308</v>
+        <v>0.7025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6986</v>
+        <v>0.294</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6697</v>
+        <v>2.1557</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6489</v>
+        <v>0.2966</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0208</v>
+        <v>1.8591</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0593</v>
+        <v>3.012</v>
       </c>
       <c r="K6" t="n">
-        <v>1.327</v>
+        <v>1.1789</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7323</v>
+        <v>1.8331</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3896</v>
+        <v>-0.8563</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6781</v>
+        <v>-0.8822</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2885</v>
+        <v>0.026</v>
       </c>
       <c r="P6" t="n">
         <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0145</v>
+        <v>-0.4346</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6534</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3611</v>
+        <v>-0.337</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6659</v>
+        <v>-0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2207</v>
+        <v>0.7147</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0733</v>
+        <v>-0.8071</v>
       </c>
       <c r="F7" t="n">
-        <v>0.294</v>
+        <v>1.5218</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1557</v>
+        <v>0.4385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2966</v>
+        <v>-0.3041</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8591</v>
+        <v>0.7427</v>
       </c>
       <c r="J7" t="n">
-        <v>3.012</v>
+        <v>0.1521</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1789</v>
+        <v>0.1021</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8331</v>
+        <v>0.0501</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8563</v>
+        <v>0.2864</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8822</v>
+        <v>-0.4062</v>
       </c>
       <c r="O7" t="n">
-        <v>0.026</v>
+        <v>0.6926</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2104</v>
+        <v>0.2761</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8734</v>
+        <v>0.2158</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.337</v>
+        <v>0.0603</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0941</v>
+        <v>-0.1654</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1387</v>
+        <v>-0.0806</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0446</v>
+        <v>-0.0848</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0608</v>
+        <v>0.2722</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5006</v>
+        <v>0.6812</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5614</v>
+        <v>-0.409</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0982</v>
+        <v>0.4598</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4287</v>
+        <v>1.0208</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.5269</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0374</v>
+        <v>-0.1875</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.3396</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9655</v>
+        <v>0.152</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9585</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2397</v>
+        <v>-0.2994</v>
       </c>
       <c r="T8" t="n">
-        <v>1.191</v>
+        <v>0.0265</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0488</v>
+        <v>-0.3258</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0564</v>
+        <v>0.0576</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0564</v>
+        <v>0.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6433</v>
+        <v>-0.9184</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3446</v>
+        <v>-4.0432</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2987</v>
+        <v>3.1248</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2722</v>
+        <v>-1.0608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6812</v>
+        <v>0.5006</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.409</v>
+        <v>-1.5614</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4598</v>
+        <v>-2.0982</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0208</v>
+        <v>0.4287</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-2.5269</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1875</v>
+        <v>1.0374</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3396</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.152</v>
+        <v>0.9655</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7773</v>
+        <v>0.4154</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2376</v>
+        <v>0.2864</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5397</v>
+        <v>0.129</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0576</v>
+        <v>-1.0564</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6083</v>
+        <v>-1.0564</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4009</v>
+        <v>-1.0405</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4277</v>
+        <v>-0.1207</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9732</v>
+        <v>-0.9197</v>
       </c>
       <c r="G10" t="n">
         <v>1.0885</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5101</v>
+        <v>-0.1497</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7546</v>
+        <v>-0.4476</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2444</v>
+        <v>0.2979</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0437</v>
+        <v>-1.6474</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1402</v>
+        <v>-4.0378</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0964</v>
+        <v>2.3905</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6064</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7126</v>
+        <v>-0.3163</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4705</v>
+        <v>-0.3682</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2421</v>
+        <v>0.0519</v>
       </c>
       <c r="V11" t="n">
         <v>0.8837</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2211</v>
+        <v>4.8151</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.4273</v>
+        <v>-9.833199999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>14.6484</v>
+        <v>14.6485</v>
       </c>
       <c r="G12" t="n">
         <v>6.0467</v>
@@ -1390,10 +1390,10 @@
         <v>13.7093</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7289</v>
+        <v>-2.135</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4056</v>
+        <v>-0.8118000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-1.3232</v>
@@ -1405,7 +1405,7 @@
         <v>2.2029</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3203999999999998</v>
+        <v>-0.3203999999999997</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4072</v>
+        <v>6.5034</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7651</v>
+        <v>3.4815</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6421</v>
+        <v>3.0219</v>
       </c>
       <c r="G13" t="n">
         <v>4.4507</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5516</v>
+        <v>0.5446</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6534</v>
+        <v>0.0629</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1019</v>
+        <v>0.4817</v>
       </c>
       <c r="V13" t="n">
         <v>0.3329</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2228</v>
+        <v>1.3086</v>
       </c>
       <c r="E14" t="n">
         <v>-1.7723</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9951</v>
+        <v>3.0809</v>
       </c>
       <c r="G14" t="n">
         <v>0.0108</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5046</v>
+        <v>0.5903</v>
       </c>
       <c r="T14" t="n">
         <v>0.2358</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2687</v>
+        <v>0.3545</v>
       </c>
       <c r="V14" t="n">
         <v>1.8825</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8084</v>
+        <v>0.1267</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1181</v>
+        <v>-1.6644</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3097</v>
+        <v>1.7911</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5744</v>
+        <v>-0.6314</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6588</v>
+        <v>-1.0916</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2332</v>
+        <v>0.4601</v>
       </c>
       <c r="J15" t="n">
-        <v>2.041</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1162</v>
+        <v>-0.0052</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1572</v>
+        <v>0.0145</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4667</v>
+        <v>-0.6407</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5427</v>
+        <v>-1.0864</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.924</v>
+        <v>0.4457</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8423</v>
+        <v>0.2075</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8973</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.945</v>
+        <v>0.2775</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8249</v>
+        <v>0.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6659</v>
+        <v>0.5507</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4432</v>
+        <v>-0.1464</v>
       </c>
       <c r="E16" t="n">
         <v>-0.2752</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.168</v>
+        <v>0.1288</v>
       </c>
       <c r="G16" t="n">
         <v>0.6281</v>
@@ -1702,13 +1702,13 @@
         <v>0.1958</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.362</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3564</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3024</v>
+        <v>-0.0056</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>P. DIAZ VALIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.623</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.744</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5249</v>
+        <v>-0.016</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1175</v>
+        <v>-1.7866</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2739</v>
+        <v>0.477</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8435</v>
+        <v>-2.2636</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6107</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.677</v>
+        <v>0.4083</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0664</v>
+        <v>-1.3241</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7281</v>
+        <v>-0.8708</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.951</v>
+        <v>0.0687</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7772</v>
+        <v>-0.9396</v>
       </c>
       <c r="P17" t="n">
         <v>0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9585</v>
+        <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3194</v>
+        <v>0.2432</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7993</v>
+        <v>0.1717</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4799</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9712</v>
+        <v>-0.7938</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2784</v>
+        <v>-0.1099</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3072</v>
+        <v>-0.6839</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6314</v>
+        <v>0.5744</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0916</v>
+        <v>-1.6588</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4601</v>
+        <v>2.2332</v>
       </c>
       <c r="J18" t="n">
-        <v>0.009299999999999999</v>
+        <v>2.041</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0052</v>
+        <v>-1.1162</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0145</v>
+        <v>3.1572</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6407</v>
+        <v>-1.4667</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0864</v>
+        <v>-0.5427</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4457</v>
+        <v>-0.924</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8905</v>
+        <v>1.2401</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.6693</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2065</v>
+        <v>0.5708</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5507</v>
+        <v>-1.8249</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5507</v>
+        <v>-0.6659</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>É. PINA HURTADO</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0219</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2141</v>
+        <v>-0.6098</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1922</v>
+        <v>-0.2576</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2649</v>
+        <v>-1.1175</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4118</v>
+        <v>-0.2739</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1468</v>
+        <v>-0.8435</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3441</v>
+        <v>0.6107</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3441</v>
+        <v>0.677</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.0664</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0791</v>
+        <v>-1.7281</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0677</v>
+        <v>-0.951</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1468</v>
+        <v>-0.7772</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0472</v>
+        <v>0.075</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3258</v>
+        <v>0.2876</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2787</v>
+        <v>-0.2126</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DIAZ VALIN</t>
+          <t>É. PINA HURTADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1159</v>
+        <v>-1.0856</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1534</v>
+        <v>-1.5211</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0375</v>
+        <v>0.4355</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7866</v>
+        <v>-1.2649</v>
       </c>
       <c r="H20" t="n">
-        <v>0.477</v>
+        <v>-1.4118</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2636</v>
+        <v>0.1468</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.3441</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4083</v>
+        <v>-1.3441</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3241</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8708</v>
+        <v>0.0791</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0687</v>
+        <v>-0.0677</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9396</v>
+        <v>0.1468</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1127</v>
+        <v>-0.0165</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2376</v>
+        <v>0.0188</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1249</v>
+        <v>-0.0353</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4903</v>
+        <v>-2.5151</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.0306</v>
+        <v>-3.5839</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5403</v>
+        <v>1.0688</v>
       </c>
       <c r="G21" t="n">
-        <v>-6.8352</v>
+        <v>-0.0751</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2627</v>
+        <v>2.8248</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.5725</v>
+        <v>-2.8999</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.1997</v>
+        <v>-0.3885</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9035</v>
+        <v>3.5029</v>
       </c>
       <c r="L21" t="n">
-        <v>-5.2962</v>
+        <v>-3.8913</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6355</v>
+        <v>0.3134</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3593</v>
+        <v>-0.6781</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7238</v>
+        <v>0.9915</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.3502</v>
       </c>
       <c r="R21" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2078</v>
+        <v>0.5001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.2439</v>
+        <v>-0.1218</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9639</v>
+        <v>0.6218</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9412</v>
+        <v>-2.5484</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2754</v>
+        <v>-0.7235</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6659</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9939</v>
+        <v>-4.627</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7096</v>
+        <v>-7.8493</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7157</v>
+        <v>3.2223</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0751</v>
+        <v>-6.8352</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8248</v>
+        <v>-2.2627</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8999</v>
+        <v>-4.5725</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3885</v>
+        <v>-6.1997</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5029</v>
+        <v>-0.9035</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.8913</v>
+        <v>-5.2962</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3134</v>
+        <v>-0.6355</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6781</v>
+        <v>-1.3593</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9915</v>
+        <v>0.7238</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.3502</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9787</v>
+        <v>1.0711</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2474</v>
+        <v>0.4252</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2687</v>
+        <v>0.6459</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.5484</v>
+        <v>0.9412</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7235</v>
+        <v>0.2754</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8249</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.221</v>
+        <v>-2.856599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.6485</v>
+        <v>-14.6484</v>
       </c>
       <c r="F23" t="n">
-        <v>10.4275</v>
+        <v>11.7918</v>
       </c>
       <c r="G23" t="n">
         <v>-6.0467</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0571</v>
+        <v>-2.057099999999999</v>
       </c>
       <c r="I23" t="n">
         <v>-3.989699999999999</v>
@@ -2227,7 +2227,7 @@
         <v>3.0309</v>
       </c>
       <c r="L23" t="n">
-        <v>-5.613600000000001</v>
+        <v>-5.6136</v>
       </c>
       <c r="M23" t="n">
         <v>-3.4642</v>
@@ -2239,7 +2239,7 @@
         <v>1.6239</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9790999999999999</v>
+        <v>0.9791000000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.7093</v>
@@ -2248,13 +2248,13 @@
         <v>14.6885</v>
       </c>
       <c r="S23" t="n">
-        <v>2.729</v>
+        <v>4.093400000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3233</v>
+        <v>1.3231</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4056</v>
+        <v>2.7702</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8826</v>
